--- a/2-5명렬표.xlsx
+++ b/2-5명렬표.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SDHS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SDHS\Desktop\Antigravity\randomseat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F56CC468-595E-44EF-B8D5-9C542D752180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DF92DE-C95A-4EF2-AA3D-8A52FEACD958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="2970" windowWidth="21600" windowHeight="11235" xr2:uid="{D1D7073B-45CB-42D3-ACF4-8C5E5EC09C07}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1D7073B-45CB-42D3-ACF4-8C5E5EC09C07}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>고병민</t>
   </si>
@@ -114,6 +114,10 @@
   </si>
   <si>
     <t>홍성민</t>
+  </si>
+  <si>
+    <t>허윤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -169,7 +173,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -201,13 +205,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -224,6 +248,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -560,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23298C3B-2C1B-4465-8C7E-5839CED0E019}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -763,6 +793,14 @@
         <v>24</v>
       </c>
     </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>27</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
